--- a/plugins/mx-core-docs/docs/orifice-calc.xlsx
+++ b/plugins/mx-core-docs/docs/orifice-calc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sam294\Documents\Projects\mx-core\plugins\mx-core-docs\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\Projects\mx-core\plugins\mx-core-docs\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{625150FB-621B-487B-849C-9BB206241D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561E8AAF-BEA6-49E1-8A71-5F46D458A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15990" windowHeight="15585" xr2:uid="{B3C35E9E-9BD3-4AD9-97FB-E1A22F9DDE03}"/>
+    <workbookView xWindow="45" yWindow="0" windowWidth="14475" windowHeight="15600" xr2:uid="{B3C35E9E-9BD3-4AD9-97FB-E1A22F9DDE03}"/>
   </bookViews>
   <sheets>
     <sheet name="orifice-design-template" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Parameter</t>
   </si>
@@ -88,16 +88,145 @@
   </si>
   <si>
     <t>Re</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>B2 = d</t>
+  </si>
+  <si>
+    <t>B3 = t</t>
+  </si>
+  <si>
+    <t>B4 = Cd</t>
+  </si>
+  <si>
+    <t>B5 = rho_air</t>
+  </si>
+  <si>
+    <t>B6 = DeltaP_Pa</t>
+  </si>
+  <si>
+    <t>B7 = Ao</t>
+  </si>
+  <si>
+    <t>B8 = t/d</t>
+  </si>
+  <si>
+    <t>B9 = Qhole_m3s</t>
+  </si>
+  <si>
+    <t>B10 = Qhole_Lmin</t>
+  </si>
+  <si>
+    <t>B11 = N</t>
+  </si>
+  <si>
+    <t>B12 = Qtotal_m3s</t>
+  </si>
+  <si>
+    <t>B13 = Qtotal_Lmin</t>
+  </si>
+  <si>
+    <t>B14 = Qtotal_m3h</t>
+  </si>
+  <si>
+    <t>Parameter,Value</t>
+  </si>
+  <si>
+    <t>d,0.001</t>
+  </si>
+  <si>
+    <t>t,0.002</t>
+  </si>
+  <si>
+    <t>Cd,0.75</t>
+  </si>
+  <si>
+    <t>rho_air,1.145</t>
+  </si>
+  <si>
+    <t>DeltaP_mmH2O,100</t>
+  </si>
+  <si>
+    <t>DeltaP_Pa,=B5*9.80665</t>
+  </si>
+  <si>
+    <t>Ao,=PI()*B2^2/4</t>
+  </si>
+  <si>
+    <t>t_d,=B3/B2</t>
+  </si>
+  <si>
+    <t>Qhole_m3s,=B4*B7*SQRT((2*B6)/B5)</t>
+  </si>
+  <si>
+    <t>Qhole_Lmin,=B9*60000</t>
+  </si>
+  <si>
+    <t>N,100</t>
+  </si>
+  <si>
+    <t>Qtotal_m3s,=B9*B11</t>
+  </si>
+  <si>
+    <t>Qtotal_Lmin,=B10*B11</t>
+  </si>
+  <si>
+    <t>Qtotal_m3h,=B12*3600</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>rho_air</t>
+  </si>
+  <si>
+    <t>DeltaP_Pa</t>
+  </si>
+  <si>
+    <t>DeltaP_mmH2O</t>
+  </si>
+  <si>
+    <t>t/d</t>
+  </si>
+  <si>
+    <t>Qhole_Lmin</t>
+  </si>
+  <si>
+    <t>Qhole_m3s</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Qtotal_m3s</t>
+  </si>
+  <si>
+    <t>Qtotal_Lmin</t>
+  </si>
+  <si>
+    <t>Qtotal_m3h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,14 +252,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -149,10 +285,12 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="2" xr16:uid="{43775168-5252-4DD6-869C-E2B3DFF5C0F8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="5">
-    <queryTableFields count="2">
+  <queryTableRefresh nextId="7" unboundColumnsRight="2">
+    <queryTableFields count="4">
       <queryTableField id="1" name="Parameter" tableColumnId="1"/>
       <queryTableField id="2" name="Value" tableColumnId="2"/>
+      <queryTableField id="5" dataBound="0" tableColumnId="3"/>
+      <queryTableField id="6" dataBound="0" tableColumnId="4"/>
     </queryTableFields>
     <queryTableDeletedFields count="2">
       <deletedField name="Formula"/>
@@ -163,11 +301,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3AC3047-E5A8-48A2-9E85-A7379F0E700F}" name="orifice_design_template__2" displayName="orifice_design_template__2" ref="A1:B15" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:B15" xr:uid="{A3AC3047-E5A8-48A2-9E85-A7379F0E700F}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6C289D1B-4884-4657-B4B6-A435B2ACCA40}" uniqueName="1" name="Parameter" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A3AC3047-E5A8-48A2-9E85-A7379F0E700F}" name="orifice_design_template__2" displayName="orifice_design_template__2" ref="A1:D15" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:D15" xr:uid="{A3AC3047-E5A8-48A2-9E85-A7379F0E700F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6C289D1B-4884-4657-B4B6-A435B2ACCA40}" uniqueName="1" name="Parameter" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{6381530D-28A7-46BA-A6FA-6DC2582C9CD2}" uniqueName="2" name="Value" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{15DBB202-766C-4976-9D07-2C019E0852DA}" uniqueName="3" name="Column1" queryTableFieldId="5"/>
+    <tableColumn id="4" xr3:uid="{F73D8FA8-4F1B-429E-926B-230212A6D9F1}" uniqueName="4" name="Column2" queryTableFieldId="6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -470,141 +610,465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95364112-2E51-4CEE-B724-CC779DC743F8}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>0.1023</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C2">
+        <v>1E-3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1E-3</v>
+      </c>
+      <c r="F2">
+        <v>1E-3</v>
+      </c>
+      <c r="G2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>6.1379999999999997E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C3">
+        <v>1E-3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2E-3</v>
+      </c>
+      <c r="F3">
+        <v>2.3E-3</v>
+      </c>
+      <c r="G3">
+        <v>2E-3</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C4">
+        <v>2E-3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>0.75</v>
+      </c>
+      <c r="F4">
+        <v>0.75</v>
+      </c>
+      <c r="G4">
+        <v>0.75</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
         <v>0.61</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="C5">
+        <v>0.75</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="1">
+        <f>1145/1000</f>
+        <v>1.145</v>
+      </c>
+      <c r="F5" s="1">
+        <f>1145/1000</f>
+        <v>1.145</v>
+      </c>
+      <c r="G5" s="1">
+        <f>1145/1000</f>
+        <v>1.145</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="C7">
+        <v>1E-3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7">
+        <f>E6*9.80665</f>
+        <v>980.66499999999996</v>
+      </c>
+      <c r="F7" s="3">
+        <f>F6*9.80665</f>
+        <v>490.33249999999998</v>
+      </c>
+      <c r="G7" s="3">
+        <f>G6*9.80665</f>
+        <v>490.33249999999998</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
         <v>13360</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="C8">
+        <v>13360</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <f>PI()*E2^2/4</f>
+        <v>7.8539816339744823E-7</v>
+      </c>
+      <c r="F8">
+        <f>PI()*F2^2/4</f>
+        <v>7.8539816339744823E-7</v>
+      </c>
+      <c r="G8">
+        <f>PI()*G2^2/4</f>
+        <v>1.9634954084936206E-7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <f>B3/B2</f>
         <v>0.6</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="C9">
+        <f>C3/C2</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9">
+        <f>E3/E2</f>
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <f>F3/F2</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G9">
+        <f>G3/G2</f>
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <f>PI()*B2^2/4</f>
         <v>8.2194195454216822E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="C10">
+        <f>PI()*C2^2/4</f>
+        <v>7.8539816339744823E-7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <f>E4*E8*SQRT((2*E7)/E5)</f>
+        <v>2.4379440643528977E-5</v>
+      </c>
+      <c r="F10" s="3">
+        <f>F4*F8*SQRT((2*F7)/F5)</f>
+        <v>1.7238867800574269E-5</v>
+      </c>
+      <c r="G10" s="3">
+        <f>G4*G8*SQRT((2*G7)/G5)</f>
+        <v>4.3097169501435673E-6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <f>PI()*B3^2/4</f>
         <v>2.958991036351805E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="C11">
+        <f>PI()*C3^2/4</f>
+        <v>7.8539816339744823E-7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <f>E10*60000</f>
+        <v>1.4627664386117387</v>
+      </c>
+      <c r="F11" s="3">
+        <f>F10*60000</f>
+        <v>1.0343320680344561</v>
+      </c>
+      <c r="G11" s="3">
+        <f>G10*60000</f>
+        <v>0.25858301700861402</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <f>B4/B3</f>
         <v>8.1459758879113719E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="C12">
+        <f>C4/C3</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13">
         <f>B5*B11*SQRT((2*B8)/(B6*(1-B9^4)))</f>
         <v>1.0000743078568707E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="C13" t="e">
+        <f>C5*C11*SQRT((2*C8)/(C6*(1-C9^4)))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <f>E10*E12</f>
+        <v>2.4379440643528976E-3</v>
+      </c>
+      <c r="F13" s="3">
+        <f>F10*F12</f>
+        <v>3.9649395941320821E-4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14">
         <f>B13/B10</f>
         <v>1.2167213296879635</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="C14" t="e">
+        <f>C13/C10</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <f>E11*E12</f>
+        <v>146.27664386117388</v>
+      </c>
+      <c r="F14" s="3">
+        <f>F11*F12</f>
+        <v>23.789637564792489</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
         <f>(B6*B14*B2)/B7</f>
         <v>124470.59202707867</v>
       </c>
+      <c r="C15" t="e">
+        <f>(C6*C14*C2)/C7</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <f>E13*3600</f>
+        <v>8.7765986316704314</v>
+      </c>
+      <c r="F15" s="3">
+        <f>F13*3600</f>
+        <v>1.4273782538875495</v>
+      </c>
+      <c r="J15" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
